--- a/data/raw/xlsx/concise.xlsx
+++ b/data/raw/xlsx/concise.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\garmin-ids\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\garmin-ids\data\raw\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3BA544-CCFC-4916-8389-F278209BCA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C509645-6B08-4C93-875A-0C4A6737926D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5504BBCC-0CF3-4847-80C4-174D6616E638}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="202">
   <si>
     <t>006-B4132-00</t>
   </si>
@@ -641,13 +641,13 @@
     <t>fēnix® 8 / quatix® 8 - 47 mm / 51 mm, AMOLED</t>
   </si>
   <si>
-    <t>epix™ Pro (Gen 2) - 47mm / quatix® 7 Pro</t>
-  </si>
-  <si>
     <t>Concise</t>
   </si>
   <si>
     <t>Part</t>
+  </si>
+  <si>
+    <t>epix™ Pro (Gen 2) - 47 mm / quatix® 7 Pro</t>
   </si>
 </sst>
 </file>
@@ -1040,10 +1040,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1436,7 +1436,7 @@
         <v>77</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>78</v>

--- a/data/raw/xlsx/concise.xlsx
+++ b/data/raw/xlsx/concise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\garmin-ids\data\raw\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C509645-6B08-4C93-875A-0C4A6737926D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EE7871-1BA5-466F-982C-B40472C61B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5504BBCC-0CF3-4847-80C4-174D6616E638}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="202">
   <si>
     <t>006-B4132-00</t>
   </si>
@@ -590,12 +590,6 @@
     <t>fēnix® 6S Pro / Sapphire</t>
   </si>
   <si>
-    <t>ForeAthlete 45 / 45S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForeAthlete 55 / Forerunner® 158 </t>
-  </si>
-  <si>
     <t>GPSMAP® 67 / 67i</t>
   </si>
   <si>
@@ -632,15 +626,9 @@
     <t>Descent™ Mk2 / Mk2i</t>
   </si>
   <si>
-    <t>fēnix® 8 Pro / quatix® 8 Pro - 47 mm / 51 mm</t>
-  </si>
-  <si>
     <t>Descent™ Mk3 / Mk3i - 43 mm</t>
   </si>
   <si>
-    <t>fēnix® 8 / quatix® 8 - 47 mm / 51 mm, AMOLED</t>
-  </si>
-  <si>
     <t>Concise</t>
   </si>
   <si>
@@ -648,6 +636,18 @@
   </si>
   <si>
     <t>epix™ Pro (Gen 2) - 47 mm / quatix® 7 Pro</t>
+  </si>
+  <si>
+    <t>ForeAthlete® 45 / 45S</t>
+  </si>
+  <si>
+    <t>fēnix® 8 Pro / quatix® 8 Pro - 47 / 51 mm</t>
+  </si>
+  <si>
+    <t>fēnix® 8 / quatix® 8 - 47 / 51 mm, AMOLED</t>
+  </si>
+  <si>
+    <t>ForeAthlete® 55 / Forerunner® 158</t>
   </si>
 </sst>
 </file>
@@ -1029,6 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DC45DCF-68BB-4103-8A17-82B1491CC1B2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1040,13 +1041,13 @@
   <sheetData>
     <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1061,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1079,7 +1080,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
@@ -1093,7 +1094,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>8</v>
@@ -1107,7 +1108,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
@@ -1116,7 +1117,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1127,7 +1128,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1138,7 +1139,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1154,7 +1155,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>24</v>
@@ -1168,7 +1169,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>27</v>
@@ -1182,7 +1183,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>30</v>
@@ -1196,7 +1197,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>30</v>
@@ -1210,7 +1211,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>34</v>
@@ -1219,7 +1220,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1239,7 +1240,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1268,7 +1269,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1288,7 +1289,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -1317,7 +1318,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -1328,7 +1329,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -1339,7 +1340,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1350,7 +1351,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -1361,7 +1362,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>64</v>
       </c>
@@ -1375,7 +1376,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -1391,7 +1392,7 @@
         <v>69</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -1408,7 +1409,7 @@
         <v>73</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>74</v>
@@ -1422,7 +1423,7 @@
         <v>76</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>74</v>
@@ -1436,7 +1437,7 @@
         <v>77</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>78</v>
@@ -1450,7 +1451,7 @@
         <v>80</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>81</v>
@@ -1467,7 +1468,7 @@
         <v>84</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>85</v>
@@ -1481,7 +1482,7 @@
         <v>87</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>88</v>
@@ -1523,7 +1524,7 @@
         <v>96</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>97</v>
@@ -1552,7 +1553,7 @@
         <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>97</v>
@@ -1573,7 +1574,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>107</v>
       </c>
@@ -1595,7 +1596,7 @@
         <v>112</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>113</v>
@@ -1615,7 +1616,7 @@
         <v>117</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>113</v>
@@ -1627,7 +1628,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>119</v>
       </c>
@@ -1641,7 +1642,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -1652,7 +1653,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -1666,7 +1667,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>129</v>
       </c>
@@ -1685,7 +1686,7 @@
         <v>133</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>134</v>
@@ -1705,7 +1706,7 @@
         <v>138</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>134</v>
@@ -1722,7 +1723,7 @@
         <v>141</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>142</v>
@@ -1736,7 +1737,7 @@
         <v>144</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>145</v>
@@ -1757,7 +1758,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>151</v>
       </c>
@@ -1768,7 +1769,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>154</v>
       </c>
@@ -1779,7 +1780,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>157</v>
       </c>
@@ -1793,7 +1794,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>160</v>
       </c>
@@ -1807,7 +1808,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>164</v>
       </c>
@@ -1818,7 +1819,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>165</v>
       </c>
@@ -1829,7 +1830,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>166</v>
       </c>
@@ -1840,7 +1841,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>169</v>
       </c>
@@ -1852,7 +1853,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J54" xr:uid="{3DC45DCF-68BB-4103-8A17-82B1491CC1B2}"/>
+  <autoFilter ref="A1:J54" xr:uid="{3DC45DCF-68BB-4103-8A17-82B1491CC1B2}">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/raw/xlsx/concise.xlsx
+++ b/data/raw/xlsx/concise.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\projects\work\garmin-ids\data\raw\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EE7871-1BA5-466F-982C-B40472C61B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD47C49-37DD-4415-B577-FE3E987D9F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5504BBCC-0CF3-4847-80C4-174D6616E638}"/>
   </bookViews>
@@ -635,9 +635,6 @@
     <t>Part</t>
   </si>
   <si>
-    <t>epix™ Pro (Gen 2) - 47 mm / quatix® 7 Pro</t>
-  </si>
-  <si>
     <t>ForeAthlete® 45 / 45S</t>
   </si>
   <si>
@@ -648,6 +645,9 @@
   </si>
   <si>
     <t>ForeAthlete® 55 / Forerunner® 158</t>
+  </si>
+  <si>
+    <t>epix™ Pro - 47 mm / quatix® 7 Pro</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1155,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>24</v>
@@ -1169,7 +1169,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>27</v>
@@ -1437,7 +1437,7 @@
         <v>77</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>78</v>
@@ -1723,7 +1723,7 @@
         <v>141</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>142</v>
@@ -1737,7 +1737,7 @@
         <v>144</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>145</v>
